--- a/grupos/6APM - Estadisticos 20232.xlsx
+++ b/grupos/6APM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="67">
   <si>
     <t>Materia</t>
   </si>
@@ -164,21 +164,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
-    <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
@@ -197,10 +197,28 @@
     <t>BAEZ</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>JOSUE EDUARDO</t>
+  </si>
+  <si>
+    <t>NAHOMI ITZAYANA</t>
+  </si>
+  <si>
+    <t>GAEL JARED</t>
   </si>
 </sst>
 </file>
@@ -708,22 +726,22 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -744,7 +762,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U4">
         <v>7</v>
@@ -756,7 +774,7 @@
         <v>9</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -785,22 +803,22 @@
         <v>7.1</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -821,7 +839,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U5">
         <v>8</v>
@@ -833,10 +851,10 @@
         <v>10</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -862,22 +880,22 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -898,7 +916,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>6</v>
@@ -907,13 +925,13 @@
         <v>5</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -939,22 +957,22 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -975,22 +993,22 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>8</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1016,22 +1034,22 @@
         <v>6</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1052,7 +1070,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>8</v>
@@ -1061,13 +1079,13 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1093,22 +1111,22 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1129,22 +1147,22 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>8</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>10</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1170,22 +1188,22 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1206,7 +1224,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U10">
         <v>7</v>
@@ -1218,7 +1236,7 @@
         <v>10</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -1247,22 +1265,22 @@
         <v>6</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1283,13 +1301,13 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U11">
         <v>9</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W11">
         <v>10</v>
@@ -1324,22 +1342,22 @@
         <v>9</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1360,16 +1378,16 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U12">
         <v>8</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X12">
         <v>9</v>
@@ -1401,22 +1419,22 @@
         <v>7</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1437,19 +1455,19 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>7</v>
@@ -1478,22 +1496,22 @@
         <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1514,7 +1532,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>6</v>
@@ -1523,13 +1541,13 @@
         <v>10</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1555,22 +1573,22 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1594,7 +1612,7 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V15">
         <v>9</v>
@@ -1603,10 +1621,10 @@
         <v>10</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1632,22 +1650,22 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1668,13 +1686,13 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>10</v>
@@ -1683,7 +1701,7 @@
         <v>9</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1709,22 +1727,22 @@
         <v>7</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1745,7 +1763,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U17">
         <v>10</v>
@@ -1760,7 +1778,7 @@
         <v>9</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1786,22 +1804,22 @@
         <v>7</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1822,13 +1840,13 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W18">
         <v>10</v>
@@ -1837,7 +1855,7 @@
         <v>10</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1863,22 +1881,22 @@
         <v>4</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -1899,7 +1917,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U19">
         <v>5</v>
@@ -1908,7 +1926,7 @@
         <v>6</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>5</v>
@@ -1940,22 +1958,22 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -1976,7 +1994,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>9</v>
@@ -1988,7 +2006,7 @@
         <v>10</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -2017,22 +2035,22 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2053,13 +2071,13 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>10</v>
@@ -2068,7 +2086,7 @@
         <v>10</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2094,22 +2112,22 @@
         <v>5</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2171,22 +2189,22 @@
         <v>9</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2207,22 +2225,22 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2248,22 +2266,22 @@
         <v>7</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2284,22 +2302,22 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V24">
         <v>9</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2325,22 +2343,22 @@
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2370,13 +2388,13 @@
         <v>10</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2402,22 +2420,22 @@
         <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2438,22 +2456,22 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2479,22 +2497,22 @@
         <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2515,10 +2533,10 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V27">
         <v>10</v>
@@ -2530,7 +2548,7 @@
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -2669,37 +2687,37 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="J4">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="K4">
         <v>100</v>
       </c>
       <c r="L4">
-        <v>86.7</v>
+        <v>92.7</v>
       </c>
       <c r="M4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N4">
         <v>100</v>
       </c>
       <c r="O4">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P4">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="Q4">
         <v>100</v>
       </c>
       <c r="R4">
-        <v>86.7</v>
+        <v>92.7</v>
       </c>
       <c r="S4">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2728,11 +2746,11 @@
         <v>100</v>
       </c>
       <c r="I5">
+        <v>98.3</v>
+      </c>
+      <c r="J5">
         <v>96.7</v>
       </c>
-      <c r="J5">
-        <v>100</v>
-      </c>
       <c r="K5">
         <v>100</v>
       </c>
@@ -2746,10 +2764,10 @@
         <v>100</v>
       </c>
       <c r="O5">
+        <v>98.3</v>
+      </c>
+      <c r="P5">
         <v>96.7</v>
-      </c>
-      <c r="P5">
-        <v>100</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -2787,37 +2805,37 @@
         <v>93.3</v>
       </c>
       <c r="I6">
-        <v>86.7</v>
+        <v>85</v>
       </c>
       <c r="J6">
-        <v>76.7</v>
+        <v>78.3</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L6">
-        <v>86.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="M6">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="N6">
         <v>93.3</v>
       </c>
       <c r="O6">
-        <v>86.7</v>
+        <v>85</v>
       </c>
       <c r="P6">
-        <v>76.7</v>
+        <v>78.3</v>
       </c>
       <c r="Q6">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R6">
-        <v>86.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="S6">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -2846,16 +2864,16 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>96.7</v>
+        <v>93.3</v>
       </c>
       <c r="J7">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="K7">
         <v>100</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M7">
         <v>100</v>
@@ -2864,16 +2882,16 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>96.7</v>
+        <v>93.3</v>
       </c>
       <c r="P7">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="Q7">
         <v>100</v>
       </c>
       <c r="R7">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -2905,16 +2923,16 @@
         <v>100</v>
       </c>
       <c r="I8">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="J8">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="K8">
         <v>100</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M8">
         <v>100</v>
@@ -2923,16 +2941,16 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="Q8">
         <v>100</v>
       </c>
       <c r="R8">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -2964,7 +2982,7 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="J9">
         <v>100</v>
@@ -2982,7 +3000,7 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -3020,7 +3038,7 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="I10">
         <v>93.3</v>
@@ -3032,13 +3050,13 @@
         <v>100</v>
       </c>
       <c r="L10">
+        <v>94.5</v>
+      </c>
+      <c r="M10">
+        <v>100</v>
+      </c>
+      <c r="N10">
         <v>96.7</v>
-      </c>
-      <c r="M10">
-        <v>100</v>
-      </c>
-      <c r="N10">
-        <v>100</v>
       </c>
       <c r="O10">
         <v>93.3</v>
@@ -3050,7 +3068,7 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>96.7</v>
+        <v>94.5</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -3079,10 +3097,10 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I11">
-        <v>93.3</v>
+        <v>91.7</v>
       </c>
       <c r="J11">
         <v>100</v>
@@ -3091,16 +3109,16 @@
         <v>100</v>
       </c>
       <c r="L11">
+        <v>94.5</v>
+      </c>
+      <c r="M11">
+        <v>100</v>
+      </c>
+      <c r="N11">
         <v>96.7</v>
       </c>
-      <c r="M11">
-        <v>100</v>
-      </c>
-      <c r="N11">
-        <v>93.3</v>
-      </c>
       <c r="O11">
-        <v>93.3</v>
+        <v>91.7</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -3109,7 +3127,7 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>96.7</v>
+        <v>94.5</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -3138,37 +3156,37 @@
         <v>100</v>
       </c>
       <c r="H12">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="I12">
-        <v>96.7</v>
+        <v>91.7</v>
       </c>
       <c r="J12">
-        <v>90</v>
+        <v>88.3</v>
       </c>
       <c r="K12">
         <v>100</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M12">
         <v>100</v>
       </c>
       <c r="N12">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="O12">
-        <v>96.7</v>
+        <v>91.7</v>
       </c>
       <c r="P12">
-        <v>90</v>
+        <v>88.3</v>
       </c>
       <c r="Q12">
         <v>100</v>
       </c>
       <c r="R12">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -3197,37 +3215,37 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="I13">
         <v>90</v>
       </c>
       <c r="J13">
+        <v>83.3</v>
+      </c>
+      <c r="K13">
+        <v>100</v>
+      </c>
+      <c r="L13">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="M13">
+        <v>100</v>
+      </c>
+      <c r="N13">
         <v>86.7</v>
-      </c>
-      <c r="K13">
-        <v>100</v>
-      </c>
-      <c r="L13">
-        <v>96.7</v>
-      </c>
-      <c r="M13">
-        <v>100</v>
-      </c>
-      <c r="N13">
-        <v>80</v>
       </c>
       <c r="O13">
         <v>90</v>
       </c>
       <c r="P13">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="Q13">
         <v>100</v>
       </c>
       <c r="R13">
-        <v>96.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -3256,7 +3274,7 @@
         <v>100</v>
       </c>
       <c r="H14">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I14">
         <v>100</v>
@@ -3274,7 +3292,7 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="O14">
         <v>100</v>
@@ -3318,10 +3336,10 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="J15">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="K15">
         <v>100</v>
@@ -3336,10 +3354,10 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P15">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -3377,7 +3395,7 @@
         <v>100</v>
       </c>
       <c r="I16">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="J16">
         <v>100</v>
@@ -3395,7 +3413,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -3551,37 +3569,37 @@
         <v>100</v>
       </c>
       <c r="H19">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I19">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="J19">
+        <v>98.3</v>
+      </c>
+      <c r="K19">
+        <v>100</v>
+      </c>
+      <c r="L19">
+        <v>94.5</v>
+      </c>
+      <c r="M19">
+        <v>100</v>
+      </c>
+      <c r="N19">
         <v>96.7</v>
       </c>
-      <c r="K19">
-        <v>100</v>
-      </c>
-      <c r="L19">
-        <v>96.7</v>
-      </c>
-      <c r="M19">
-        <v>100</v>
-      </c>
-      <c r="N19">
-        <v>93.3</v>
-      </c>
       <c r="O19">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="P19">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="Q19">
         <v>100</v>
       </c>
       <c r="R19">
-        <v>96.7</v>
+        <v>94.5</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -3613,16 +3631,16 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="J20">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K20">
         <v>100</v>
       </c>
       <c r="L20">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M20">
         <v>100</v>
@@ -3631,16 +3649,16 @@
         <v>100</v>
       </c>
       <c r="O20">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P20">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q20">
         <v>100</v>
       </c>
       <c r="R20">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -3672,7 +3690,7 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="J21">
         <v>100</v>
@@ -3690,7 +3708,7 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -3731,37 +3749,37 @@
         <v>80</v>
       </c>
       <c r="I22">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J22">
-        <v>53.3</v>
+        <v>26.7</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L22">
-        <v>13.3</v>
+        <v>7.3</v>
       </c>
       <c r="M22">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="N22">
         <v>80</v>
       </c>
       <c r="O22">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P22">
-        <v>53.3</v>
+        <v>26.7</v>
       </c>
       <c r="Q22">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="R22">
-        <v>13.3</v>
+        <v>7.3</v>
       </c>
       <c r="S22">
-        <v>48</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -3787,40 +3805,40 @@
         <v>100</v>
       </c>
       <c r="H23">
+        <v>90</v>
+      </c>
+      <c r="I23">
+        <v>91.7</v>
+      </c>
+      <c r="J23">
         <v>80</v>
       </c>
-      <c r="I23">
+      <c r="K23">
+        <v>100</v>
+      </c>
+      <c r="L23">
+        <v>94.5</v>
+      </c>
+      <c r="M23">
         <v>90</v>
       </c>
-      <c r="J23">
-        <v>73.3</v>
-      </c>
-      <c r="K23">
-        <v>100</v>
-      </c>
-      <c r="L23">
-        <v>96.7</v>
-      </c>
-      <c r="M23">
-        <v>100</v>
-      </c>
       <c r="N23">
+        <v>90</v>
+      </c>
+      <c r="O23">
+        <v>91.7</v>
+      </c>
+      <c r="P23">
         <v>80</v>
       </c>
-      <c r="O23">
+      <c r="Q23">
+        <v>100</v>
+      </c>
+      <c r="R23">
+        <v>94.5</v>
+      </c>
+      <c r="S23">
         <v>90</v>
-      </c>
-      <c r="P23">
-        <v>73.3</v>
-      </c>
-      <c r="Q23">
-        <v>100</v>
-      </c>
-      <c r="R23">
-        <v>96.7</v>
-      </c>
-      <c r="S23">
-        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -3846,37 +3864,37 @@
         <v>100</v>
       </c>
       <c r="H24">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I24">
+        <v>98.3</v>
+      </c>
+      <c r="J24">
+        <v>91.7</v>
+      </c>
+      <c r="K24">
+        <v>90</v>
+      </c>
+      <c r="L24">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="M24">
+        <v>100</v>
+      </c>
+      <c r="N24">
         <v>96.7</v>
       </c>
-      <c r="J24">
-        <v>83.3</v>
-      </c>
-      <c r="K24">
-        <v>100</v>
-      </c>
-      <c r="L24">
-        <v>93.3</v>
-      </c>
-      <c r="M24">
-        <v>100</v>
-      </c>
-      <c r="N24">
-        <v>93.3</v>
-      </c>
       <c r="O24">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P24">
-        <v>83.3</v>
+        <v>91.7</v>
       </c>
       <c r="Q24">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R24">
-        <v>93.3</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -3905,37 +3923,37 @@
         <v>100</v>
       </c>
       <c r="H25">
+        <v>96.7</v>
+      </c>
+      <c r="I25">
         <v>93.3</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>96.7</v>
       </c>
-      <c r="J25">
+      <c r="K25">
+        <v>100</v>
+      </c>
+      <c r="L25">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="M25">
+        <v>100</v>
+      </c>
+      <c r="N25">
+        <v>96.7</v>
+      </c>
+      <c r="O25">
         <v>93.3</v>
       </c>
-      <c r="K25">
-        <v>100</v>
-      </c>
-      <c r="L25">
-        <v>93.3</v>
-      </c>
-      <c r="M25">
-        <v>100</v>
-      </c>
-      <c r="N25">
-        <v>93.3</v>
-      </c>
-      <c r="O25">
+      <c r="P25">
         <v>96.7</v>
       </c>
-      <c r="P25">
-        <v>93.3</v>
-      </c>
       <c r="Q25">
         <v>100</v>
       </c>
       <c r="R25">
-        <v>93.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -3976,7 +3994,7 @@
         <v>100</v>
       </c>
       <c r="L26">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
       <c r="M26">
         <v>100</v>
@@ -3994,7 +4012,7 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -4113,7 +4131,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>48</v>
@@ -4122,19 +4140,19 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2">
-        <v>87.5</v>
+        <v>79.2</v>
       </c>
       <c r="G2" s="2">
-        <v>12.5</v>
+        <v>20.8</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4145,7 +4163,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
@@ -4166,7 +4184,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4177,7 +4195,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
@@ -4198,7 +4216,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4209,7 +4227,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
@@ -4230,7 +4248,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4241,7 +4259,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
@@ -4250,19 +4268,19 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="G6" s="2">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>9.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4294,7 +4312,7 @@
         <v>4.2</v>
       </c>
       <c r="H7">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4344,7 +4362,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4382,16 +4400,16 @@
         <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4405,18 +4423,64 @@
         <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>48</v>
       </c>
       <c r="G3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920335</v>
+      </c>
+      <c r="B4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920137</v>
+      </c>
+      <c r="B5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6APM - Estadisticos 20232.xlsx
+++ b/grupos/6APM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="58">
   <si>
     <t>Materia</t>
   </si>
@@ -164,24 +164,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -192,33 +192,6 @@
   </si>
   <si>
     <t>Nombres</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>JOSUE EDUARDO</t>
-  </si>
-  <si>
-    <t>NAHOMI ITZAYANA</t>
-  </si>
-  <si>
-    <t>GAEL JARED</t>
   </si>
 </sst>
 </file>
@@ -744,22 +717,22 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
         <v>9</v>
@@ -768,7 +741,7 @@
         <v>7</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W4">
         <v>9</v>
@@ -821,22 +794,22 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
         <v>9</v>
@@ -854,7 +827,7 @@
         <v>9</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -898,40 +871,40 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U6">
         <v>6</v>
       </c>
       <c r="V6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>6</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -975,22 +948,22 @@
         <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>9</v>
@@ -1008,7 +981,7 @@
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1052,22 +1025,22 @@
         <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1129,28 +1102,28 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>9</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -1162,7 +1135,7 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1206,28 +1179,28 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>9</v>
@@ -1283,22 +1256,22 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1360,22 +1333,22 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
         <v>9</v>
@@ -1437,25 +1410,25 @@
         <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>7</v>
@@ -1467,7 +1440,7 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>7</v>
@@ -1514,28 +1487,28 @@
         <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
         <v>9</v>
       </c>
       <c r="U14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>10</v>
@@ -1544,7 +1517,7 @@
         <v>9</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>7</v>
@@ -1591,22 +1564,22 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -1615,7 +1588,7 @@
         <v>9</v>
       </c>
       <c r="V15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>10</v>
@@ -1668,25 +1641,25 @@
         <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16">
         <v>8</v>
@@ -1701,7 +1674,7 @@
         <v>9</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1745,22 +1718,22 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -1822,22 +1795,22 @@
         <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>9</v>
@@ -1855,7 +1828,7 @@
         <v>10</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1899,40 +1872,40 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>7</v>
       </c>
       <c r="U19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>7</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1976,22 +1949,22 @@
         <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
         <v>9</v>
@@ -2053,28 +2026,28 @@
         <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>10</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>9</v>
@@ -2130,22 +2103,22 @@
         <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
         <v>5</v>
@@ -2207,40 +2180,40 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
         <v>10</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V23">
         <v>8</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2284,25 +2257,25 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U24">
         <v>9</v>
@@ -2314,7 +2287,7 @@
         <v>9</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>9</v>
@@ -2361,22 +2334,22 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2438,22 +2411,22 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>9</v>
@@ -2515,22 +2488,22 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2702,22 +2675,22 @@
         <v>90</v>
       </c>
       <c r="N4">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O4">
-        <v>98.3</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P4">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q4">
         <v>100</v>
       </c>
       <c r="R4">
-        <v>92.7</v>
+        <v>95</v>
       </c>
       <c r="S4">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2761,13 +2734,13 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O5">
-        <v>98.3</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P5">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -2820,22 +2793,22 @@
         <v>70</v>
       </c>
       <c r="N6">
-        <v>93.3</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="O6">
-        <v>85</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="P6">
-        <v>78.3</v>
+        <v>84.7</v>
       </c>
       <c r="Q6">
-        <v>80</v>
+        <v>93.8</v>
       </c>
       <c r="R6">
-        <v>83.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="S6">
-        <v>70</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -2879,19 +2852,19 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O7">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="P7">
-        <v>93.3</v>
+        <v>95.3</v>
       </c>
       <c r="Q7">
         <v>100</v>
       </c>
       <c r="R7">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -2938,19 +2911,19 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O8">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P8">
-        <v>93.3</v>
+        <v>95.3</v>
       </c>
       <c r="Q8">
         <v>100</v>
       </c>
       <c r="R8">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -3000,7 +2973,7 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -3056,10 +3029,10 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>96.7</v>
+        <v>95.8</v>
       </c>
       <c r="O10">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -3068,7 +3041,7 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -3115,10 +3088,10 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>96.7</v>
+        <v>95.8</v>
       </c>
       <c r="O11">
-        <v>91.7</v>
+        <v>93.8</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -3127,7 +3100,7 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -3174,19 +3147,19 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>93.3</v>
+        <v>91.7</v>
       </c>
       <c r="O12">
-        <v>91.7</v>
+        <v>94.8</v>
       </c>
       <c r="P12">
-        <v>88.3</v>
+        <v>91.8</v>
       </c>
       <c r="Q12">
         <v>100</v>
       </c>
       <c r="R12">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -3233,19 +3206,19 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>86.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="O13">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="P13">
-        <v>83.3</v>
+        <v>88.2</v>
       </c>
       <c r="Q13">
         <v>100</v>
       </c>
       <c r="R13">
-        <v>96.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -3292,7 +3265,7 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O14">
         <v>100</v>
@@ -3354,10 +3327,10 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="P15">
-        <v>93.3</v>
+        <v>95.3</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -3413,7 +3386,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -3587,19 +3560,19 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O19">
-        <v>91.7</v>
+        <v>94.8</v>
       </c>
       <c r="P19">
-        <v>98.3</v>
+        <v>98.8</v>
       </c>
       <c r="Q19">
         <v>100</v>
       </c>
       <c r="R19">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -3649,16 +3622,16 @@
         <v>100</v>
       </c>
       <c r="O20">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="P20">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q20">
         <v>100</v>
       </c>
       <c r="R20">
-        <v>96.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -3708,7 +3681,7 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -3764,22 +3737,22 @@
         <v>26</v>
       </c>
       <c r="N22">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="O22">
-        <v>30</v>
+        <v>18.8</v>
       </c>
       <c r="P22">
-        <v>26.7</v>
+        <v>18.8</v>
       </c>
       <c r="Q22">
-        <v>50</v>
+        <v>31.3</v>
       </c>
       <c r="R22">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="S22">
-        <v>26</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -3823,22 +3796,22 @@
         <v>90</v>
       </c>
       <c r="N23">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="O23">
-        <v>91.7</v>
+        <v>94.8</v>
       </c>
       <c r="P23">
-        <v>80</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q23">
         <v>100</v>
       </c>
       <c r="R23">
-        <v>94.5</v>
+        <v>95</v>
       </c>
       <c r="S23">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -3882,19 +3855,19 @@
         <v>100</v>
       </c>
       <c r="N24">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O24">
-        <v>98.3</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P24">
-        <v>91.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="Q24">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R24">
-        <v>89.09999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -3941,19 +3914,19 @@
         <v>100</v>
       </c>
       <c r="N25">
-        <v>96.7</v>
+        <v>95.8</v>
       </c>
       <c r="O25">
-        <v>93.3</v>
+        <v>94.8</v>
       </c>
       <c r="P25">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q25">
         <v>100</v>
       </c>
       <c r="R25">
-        <v>90.90000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -4012,7 +3985,7 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -4131,7 +4104,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>48</v>
@@ -4140,19 +4113,19 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2">
-        <v>79.2</v>
+        <v>95.8</v>
       </c>
       <c r="G2" s="2">
-        <v>20.8</v>
+        <v>4.2</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>8.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4172,16 +4145,16 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="G3" s="2">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="H3">
         <v>8</v>
@@ -4204,16 +4177,16 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="G4" s="2">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="H4">
         <v>8.4</v>
@@ -4227,7 +4200,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
@@ -4236,19 +4209,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="G5" s="2">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4259,7 +4232,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
@@ -4280,7 +4253,7 @@
         <v>4.2</v>
       </c>
       <c r="H6">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4291,7 +4264,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>53</v>
@@ -4312,7 +4285,7 @@
         <v>4.2</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4362,7 +4335,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4392,98 +4365,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920334</v>
-      </c>
-      <c r="B2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920334</v>
-      </c>
-      <c r="B3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920335</v>
-      </c>
-      <c r="B4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920137</v>
-      </c>
-      <c r="B5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
